--- a/从零开始学Slots/从零开始学Slots-06-数值篇-3x5LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-06-数值篇-3x5LineSlots.xlsx
@@ -5134,6 +5134,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N113" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6104,5 +6107,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M80" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-06-数值篇-3x5LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-06-数值篇-3x5LineSlots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="135">
   <si>
     <r>
       <rPr>
@@ -4300,7 +4300,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4443,6 +4443,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5195,8 +5203,8 @@
       <c r="B5" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>75</v>
+      <c r="C5" s="36">
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6051,8 +6059,8 @@
         <f aca="false">IF(SUM(C32:C40)&lt;=$B$10,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C57" s="20" t="s">
-        <v>132</v>
+      <c r="C57" s="37">
+        <v>3</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>

--- a/从零开始学Slots/从零开始学Slots-06-数值篇-3x5LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-06-数值篇-3x5LineSlots.xlsx
@@ -4111,12 +4111,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -4300,7 +4301,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4450,6 +4451,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5644,7 +5657,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="38" t="n">
         <f aca="false">C32/D32</f>
         <v>0.0246913580246914</v>
       </c>
@@ -5671,7 +5684,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="38" t="n">
         <f aca="false">C33/D33</f>
         <v>0.00823045267489712</v>
       </c>
@@ -5698,7 +5711,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E34" s="22" t="n">
+      <c r="E34" s="38" t="n">
         <f aca="false">C34/D34</f>
         <v>0.00411522633744856</v>
       </c>
@@ -5725,7 +5738,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E35" s="22" t="n">
+      <c r="E35" s="38" t="n">
         <f aca="false">C35/D35</f>
         <v>0.0246913580246914</v>
       </c>
@@ -5752,7 +5765,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E36" s="22" t="n">
+      <c r="E36" s="38" t="n">
         <f aca="false">C36/D36</f>
         <v>0.00823045267489712</v>
       </c>
@@ -5779,7 +5792,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E37" s="22" t="n">
+      <c r="E37" s="38" t="n">
         <f aca="false">C37/D37</f>
         <v>0.00411522633744856</v>
       </c>
@@ -5806,7 +5819,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E38" s="22" t="n">
+      <c r="E38" s="38" t="n">
         <f aca="false">C38/D38</f>
         <v>0.0246913580246914</v>
       </c>
@@ -5833,7 +5846,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E39" s="22" t="n">
+      <c r="E39" s="38" t="n">
         <f aca="false">C39/D39</f>
         <v>0.00823045267489712</v>
       </c>
@@ -5860,7 +5873,7 @@
         <f aca="false">$B$10</f>
         <v>7776</v>
       </c>
-      <c r="E40" s="22" t="n">
+      <c r="E40" s="38" t="n">
         <f aca="false">C40/D40</f>
         <v>0.00411522633744856</v>
       </c>
@@ -5936,7 +5949,7 @@
       <c r="A46" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B46" s="27" t="n">
+      <c r="B46" s="39" t="n">
         <f aca="false">G41</f>
         <v>0.930041152263375</v>
       </c>
